--- a/artfynd/A 31613-2025 artfynd.xlsx
+++ b/artfynd/A 31613-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,6 +1265,1533 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126394282</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>479918</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6857324</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126394531</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>479870</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6857245</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126379673</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80080</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480754</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6856633</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126379680</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>480204</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6856682</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126396419</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98256</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>479889</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6857242</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126379681</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>480475</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6856759</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126394636</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80080</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>479799</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6857259</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126379671</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97236</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kropptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>479829</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6857267</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126379672</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80081</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>480757</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6856633</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126379678</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80081</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>480243</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6856877</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126395812</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97236</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>480181</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6856903</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126394315</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97236</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>479898</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6857330</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126379677</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97236</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>480386</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6856923</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126379676</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>480175</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6856642</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126394344</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>479882</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6857332</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31613-2025 artfynd.xlsx
+++ b/artfynd/A 31613-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126368298</v>
+        <v>126369322</v>
       </c>
       <c r="B6" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,37 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480764</v>
+        <v>480591</v>
       </c>
       <c r="R6" t="n">
-        <v>6856584</v>
+        <v>6856763</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126369322</v>
+        <v>126368298</v>
       </c>
       <c r="B7" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,37 +1181,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480591</v>
+        <v>480764</v>
       </c>
       <c r="R7" t="n">
-        <v>6856763</v>
+        <v>6856584</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126379681</v>
+        <v>126394636</v>
       </c>
       <c r="B13" t="n">
-        <v>78735</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,41 +1781,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480475</v>
+        <v>479799</v>
       </c>
       <c r="R13" t="n">
-        <v>6856759</v>
+        <v>6857259</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1839,17 +1835,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,22 +1855,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126394636</v>
+        <v>126379681</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>78735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,37 +1878,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479799</v>
+        <v>480475</v>
       </c>
       <c r="R14" t="n">
-        <v>6857259</v>
+        <v>6856759</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1941,12 +1936,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1961,12 +1961,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126395812</v>
+        <v>126394315</v>
       </c>
       <c r="B18" t="n">
         <v>97236</v>
@@ -2322,17 +2322,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480181</v>
+        <v>479898</v>
       </c>
       <c r="R18" t="n">
-        <v>6856903</v>
+        <v>6857330</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126394315</v>
+        <v>126395812</v>
       </c>
       <c r="B19" t="n">
         <v>97236</v>
@@ -2419,17 +2419,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479898</v>
+        <v>480181</v>
       </c>
       <c r="R19" t="n">
-        <v>6857330</v>
+        <v>6856903</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126379676</v>
+        <v>126394344</v>
       </c>
       <c r="B21" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,41 +2602,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480175</v>
+        <v>479882</v>
       </c>
       <c r="R21" t="n">
-        <v>6856642</v>
+        <v>6857332</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2660,17 +2656,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,22 +2676,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126394344</v>
+        <v>126379676</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2708,37 +2699,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479882</v>
+        <v>480175</v>
       </c>
       <c r="R22" t="n">
-        <v>6857332</v>
+        <v>6856642</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2762,12 +2757,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,12 +2782,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 31613-2025 artfynd.xlsx
+++ b/artfynd/A 31613-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126369182</v>
       </c>
       <c r="B2" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126368446</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126368189</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126370164</v>
       </c>
       <c r="B5" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126369322</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>126368298</v>
       </c>
       <c r="B7" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>126394282</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126394531</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126379673</v>
+        <v>126379680</v>
       </c>
       <c r="B10" t="n">
-        <v>80080</v>
+        <v>98278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480754</v>
+        <v>480204</v>
       </c>
       <c r="R10" t="n">
-        <v>6856633</v>
+        <v>6856682</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126379680</v>
+        <v>126379673</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
+        <v>80083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480204</v>
+        <v>480754</v>
       </c>
       <c r="R11" t="n">
-        <v>6856682</v>
+        <v>6856633</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1676,7 +1676,7 @@
         <v>126396419</v>
       </c>
       <c r="B12" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>126394636</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126379681</v>
       </c>
       <c r="B14" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>126379671</v>
       </c>
       <c r="B15" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>126379672</v>
       </c>
       <c r="B16" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,52 +2185,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126379678</v>
+        <v>126394315</v>
       </c>
       <c r="B17" t="n">
-        <v>80081</v>
+        <v>97245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480243</v>
+        <v>479898</v>
       </c>
       <c r="R17" t="n">
-        <v>6856877</v>
+        <v>6857330</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2254,17 +2250,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2279,22 +2270,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126394315</v>
+        <v>126395812</v>
       </c>
       <c r="B18" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2322,17 +2313,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479898</v>
+        <v>480181</v>
       </c>
       <c r="R18" t="n">
-        <v>6857330</v>
+        <v>6856903</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,48 +2379,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126395812</v>
+        <v>126379678</v>
       </c>
       <c r="B19" t="n">
-        <v>97236</v>
+        <v>80084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480181</v>
+        <v>480243</v>
       </c>
       <c r="R19" t="n">
-        <v>6856903</v>
+        <v>6856877</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2453,12 +2448,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2473,12 +2473,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2488,7 +2488,7 @@
         <v>126379677</v>
       </c>
       <c r="B20" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>126394344</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>126379676</v>
       </c>
       <c r="B22" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 31613-2025 artfynd.xlsx
+++ b/artfynd/A 31613-2025 artfynd.xlsx
@@ -2591,10 +2591,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126394344</v>
+        <v>126379676</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,37 +2602,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479882</v>
+        <v>480175</v>
       </c>
       <c r="R21" t="n">
-        <v>6857332</v>
+        <v>6856642</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2656,12 +2660,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2676,22 +2685,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126379676</v>
+        <v>126394344</v>
       </c>
       <c r="B22" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2699,41 +2708,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480175</v>
+        <v>479882</v>
       </c>
       <c r="R22" t="n">
-        <v>6856642</v>
+        <v>6857332</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2757,17 +2762,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,12 +2782,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 31613-2025 artfynd.xlsx
+++ b/artfynd/A 31613-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126369322</v>
+        <v>126368298</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,37 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480591</v>
+        <v>480764</v>
       </c>
       <c r="R6" t="n">
-        <v>6856763</v>
+        <v>6856584</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126368298</v>
+        <v>126369322</v>
       </c>
       <c r="B7" t="n">
-        <v>80084</v>
+        <v>80083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,37 +1181,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480764</v>
+        <v>480591</v>
       </c>
       <c r="R7" t="n">
-        <v>6856584</v>
+        <v>6856763</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2282,48 +2282,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126395812</v>
+        <v>126379678</v>
       </c>
       <c r="B18" t="n">
-        <v>97245</v>
+        <v>80084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480181</v>
+        <v>480243</v>
       </c>
       <c r="R18" t="n">
-        <v>6856903</v>
+        <v>6856877</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2347,12 +2351,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2367,64 +2376,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126379678</v>
+        <v>126395812</v>
       </c>
       <c r="B19" t="n">
-        <v>80084</v>
+        <v>97245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480243</v>
+        <v>480181</v>
       </c>
       <c r="R19" t="n">
-        <v>6856877</v>
+        <v>6856903</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2448,17 +2453,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2473,12 +2473,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126379676</v>
+        <v>126394344</v>
       </c>
       <c r="B21" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,41 +2602,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480175</v>
+        <v>479882</v>
       </c>
       <c r="R21" t="n">
-        <v>6856642</v>
+        <v>6857332</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2660,17 +2656,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,22 +2676,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126394344</v>
+        <v>126379676</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2708,37 +2699,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479882</v>
+        <v>480175</v>
       </c>
       <c r="R22" t="n">
-        <v>6857332</v>
+        <v>6856642</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2762,12 +2757,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,12 +2782,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 31613-2025 artfynd.xlsx
+++ b/artfynd/A 31613-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126369182</v>
+        <v>126379678</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480605</v>
+        <v>480243</v>
       </c>
       <c r="R2" t="n">
-        <v>6856738</v>
+        <v>6856877</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,26 +769,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126368446</v>
+        <v>126394344</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -808,14 +812,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480752</v>
+        <v>479882</v>
       </c>
       <c r="R3" t="n">
-        <v>6856649</v>
+        <v>6857332</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -842,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,45 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126368189</v>
+        <v>126394531</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480740</v>
+        <v>479870</v>
       </c>
       <c r="R4" t="n">
-        <v>6856561</v>
+        <v>6857245</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -939,17 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växande på asp.</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126370164</v>
+        <v>126379681</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,37 +986,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480391</v>
+        <v>480475</v>
       </c>
       <c r="R5" t="n">
-        <v>6856650</v>
+        <v>6856759</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1041,12 +1044,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,22 +1069,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126368298</v>
+        <v>126394636</v>
       </c>
       <c r="B6" t="n">
-        <v>80084</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,34 +1092,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480764</v>
+        <v>479799</v>
       </c>
       <c r="R6" t="n">
-        <v>6856584</v>
+        <v>6857259</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1138,12 +1146,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126369322</v>
+        <v>126395367</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,13 +1213,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480591</v>
+        <v>479919</v>
       </c>
       <c r="R7" t="n">
-        <v>6856763</v>
+        <v>6856964</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1235,12 +1243,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126394282</v>
+        <v>126370835</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1286,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479918</v>
+        <v>480320</v>
       </c>
       <c r="R8" t="n">
-        <v>6857324</v>
+        <v>6856523</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1332,12 +1340,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126394531</v>
+        <v>126370164</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,34 +1383,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479870</v>
+        <v>480391</v>
       </c>
       <c r="R9" t="n">
-        <v>6857245</v>
+        <v>6856650</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1429,12 +1437,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1464,7 +1472,7 @@
         <v>126379680</v>
       </c>
       <c r="B10" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,52 +1575,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126379673</v>
+        <v>126394249</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480754</v>
+        <v>479933</v>
       </c>
       <c r="R11" t="n">
-        <v>6856633</v>
+        <v>6857313</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1636,17 +1640,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1661,22 +1660,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126396419</v>
+        <v>126394282</v>
       </c>
       <c r="B12" t="n">
-        <v>98265</v>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479889</v>
+        <v>479918</v>
       </c>
       <c r="R12" t="n">
-        <v>6857242</v>
+        <v>6857324</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1770,32 +1769,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126394636</v>
+        <v>126396419</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>99022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479799</v>
+        <v>479889</v>
       </c>
       <c r="R13" t="n">
-        <v>6857259</v>
+        <v>6857242</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1867,32 +1866,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126379681</v>
+        <v>126379671</v>
       </c>
       <c r="B14" t="n">
-        <v>78738</v>
+        <v>97989</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1902,17 +1901,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Kropptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480475</v>
+        <v>479829</v>
       </c>
       <c r="R14" t="n">
-        <v>6856759</v>
+        <v>6857267</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1936,12 +1935,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1973,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126379671</v>
+        <v>126379675</v>
       </c>
       <c r="B15" t="n">
-        <v>97245</v>
+        <v>97989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,14 +2007,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kropptjärn, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479829</v>
+        <v>480247</v>
       </c>
       <c r="R15" t="n">
-        <v>6857267</v>
+        <v>6856638</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,12 +2041,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2079,32 +2078,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126379672</v>
+        <v>126379677</v>
       </c>
       <c r="B16" t="n">
-        <v>80084</v>
+        <v>97989</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2118,13 +2117,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480757</v>
+        <v>480386</v>
       </c>
       <c r="R16" t="n">
-        <v>6856633</v>
+        <v>6856923</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2148,12 +2147,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2188,7 +2187,7 @@
         <v>126394315</v>
       </c>
       <c r="B17" t="n">
-        <v>97245</v>
+        <v>97989</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,52 +2281,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126379678</v>
+        <v>126395812</v>
       </c>
       <c r="B18" t="n">
-        <v>80084</v>
+        <v>97989</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480243</v>
+        <v>480181</v>
       </c>
       <c r="R18" t="n">
-        <v>6856877</v>
+        <v>6856903</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2351,17 +2346,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2376,60 +2366,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126395812</v>
+        <v>126379676</v>
       </c>
       <c r="B19" t="n">
-        <v>97245</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tyckelåsen, Tyckelåsen, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480181</v>
+        <v>480175</v>
       </c>
       <c r="R19" t="n">
-        <v>6856903</v>
+        <v>6856642</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2453,12 +2447,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2473,64 +2472,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126379677</v>
+        <v>126368298</v>
       </c>
       <c r="B20" t="n">
-        <v>97245</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480386</v>
+        <v>480764</v>
       </c>
       <c r="R20" t="n">
-        <v>6856923</v>
+        <v>6856584</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2554,17 +2549,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2579,22 +2569,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126394344</v>
+        <v>126379672</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,37 +2592,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479882</v>
+        <v>480757</v>
       </c>
       <c r="R21" t="n">
-        <v>6857332</v>
+        <v>6856633</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2656,12 +2650,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2676,64 +2675,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126379676</v>
+        <v>126368314</v>
       </c>
       <c r="B22" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480175</v>
+        <v>480765</v>
       </c>
       <c r="R22" t="n">
-        <v>6856642</v>
+        <v>6856563</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2757,17 +2752,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,15 +2772,616 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126368446</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>480752</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6856649</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126368189</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>480740</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6856561</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växande på asp.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126368301</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>480762</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6856577</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126369322</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sundtjärnsmyran, Sundtjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>480591</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6856763</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126379673</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>480754</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6856633</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126369182</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sundtjärnen, Sundtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>480605</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6856738</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31613-2025 artfynd.xlsx
+++ b/artfynd/A 31613-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126368298</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379678</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126368314</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126368446</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126394344</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126394531</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379681</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126368189</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126368301</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126369322</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1877,6 +1937,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379673</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126394636</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2071,6 +2141,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126395367</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2173,6 +2248,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126369182</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2270,6 +2350,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126370835</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2367,6 +2452,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126370164</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2473,6 +2563,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379680</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2570,6 +2665,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126394249</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2667,6 +2767,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126394282</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2764,6 +2869,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126396419</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2870,6 +2980,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379671</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2976,6 +3091,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379675</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3082,6 +3202,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379677</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3179,6 +3304,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126394315</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3276,6 +3406,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126395812</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3382,8 +3517,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>